--- a/results/greedy/UAVs7_GRID13/tour/UAVs7_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs7_GRID13/tour/UAVs7_GRID13_1920_16_Greedy_sequences.xlsx
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02850116696208715</v>
+        <v>0.02852812496712431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01911404199199751</v>
+        <v>0.01897354196989909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932983299251646</v>
+        <v>0.02911925001535565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02353062498150393</v>
+        <v>0.02330266596982256</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495987497968599</v>
+        <v>0.02339345903601497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02856179204536602</v>
+        <v>0.02857024996774271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02618170797359198</v>
+        <v>0.02555333299096674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03304312500404194</v>
+        <v>0.03203679202124476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03112479095580056</v>
+        <v>0.0302285419893451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03636895801173523</v>
+        <v>0.03372145799221471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02845650003291667</v>
+        <v>0.02658058301312849</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02202862501144409</v>
+        <v>0.01939066703198478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02200649998849258</v>
+        <v>0.02140924998093396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02491870796075091</v>
+        <v>0.0252443749923259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02889750001486391</v>
+        <v>0.02933533402392641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02814187499461696</v>
+        <v>0.02849187498213723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02365149999968708</v>
+        <v>0.02431420801440254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02482166700065136</v>
+        <v>0.02578016702318564</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02104024996515363</v>
+        <v>0.02154920803150162</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02229533396894112</v>
+        <v>0.02216866600792855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495991601608694</v>
+        <v>0.02485666604479775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0299267919617705</v>
+        <v>0.02986958401743323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02233208401594311</v>
+        <v>0.02219666697783396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0318064580205828</v>
+        <v>0.02972183300880715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02324329200200737</v>
+        <v>0.02358320803614333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02800524997292086</v>
+        <v>0.04944491700734943</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02480299997841939</v>
+        <v>0.02598287496948615</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03025483398232609</v>
+        <v>0.03095074999146163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02384729101322591</v>
+        <v>0.02550279203569517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03262499999254942</v>
+        <v>0.03195412497734651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02311074995668605</v>
+        <v>0.02267245895927772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02724283403949812</v>
+        <v>0.0279294170322828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240470829885453</v>
+        <v>0.02425133297219872</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02602020796621218</v>
+        <v>0.02588825003476813</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03089058300247416</v>
+        <v>0.03018983302172273</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.023938917031046</v>
+        <v>0.0237080420483835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02716904203407466</v>
+        <v>0.02656441699946299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02714987500803545</v>
+        <v>0.02877283398993313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02376283303601667</v>
+        <v>0.02457995899021626</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02408762503182516</v>
+        <v>0.02401875000214204</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02306445798603818</v>
+        <v>0.02454429201316088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02089679200435057</v>
+        <v>0.02123129100073129</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0205520840245299</v>
+        <v>0.0211400410044007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02680837496882305</v>
+        <v>0.02739004197064787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03148791700368747</v>
+        <v>0.03163108398439363</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02977504197042435</v>
+        <v>0.03179404098773375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02701929199974984</v>
+        <v>0.02764237497467548</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02494612499140203</v>
+        <v>0.0251111249672249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02700095798354596</v>
+        <v>0.02512137498706579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03137962496839464</v>
+        <v>0.03190458397148177</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650041703600436</v>
+        <v>0.02628262504003942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02756283304188401</v>
+        <v>0.02713574998779222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01847262500086799</v>
+        <v>0.01829141698544845</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0261859159800224</v>
+        <v>0.02545687498059124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02611487498506904</v>
+        <v>0.02600558404810727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02493795804912224</v>
+        <v>0.02497183397645131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02269658300792798</v>
+        <v>0.0239355830126442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02853524999227375</v>
+        <v>0.02783191698836163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0321460830164142</v>
+        <v>0.03186837502289563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02348929102299735</v>
+        <v>0.02364387502893806</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03064358397386968</v>
+        <v>0.02974949998315424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02356037497520447</v>
+        <v>0.02305916702607647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02482674998464063</v>
+        <v>0.02459537499817088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02090649999445304</v>
+        <v>0.02201074996264651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02925620798487216</v>
+        <v>0.03043645800789818</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02726695901947096</v>
+        <v>0.02690733299823478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02708187501411885</v>
+        <v>0.02887920796638355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02575874998001382</v>
+        <v>0.02733545901719481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03181741700973362</v>
+        <v>0.03215612500207499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02272566698957235</v>
+        <v>0.02387554198503494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072112501831725</v>
+        <v>0.03116479102754965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02772083401214331</v>
+        <v>0.02964449999853969</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03420033399015665</v>
+        <v>0.03816629201173782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03040112502640113</v>
+        <v>0.02985245804302394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02760583302006125</v>
+        <v>0.02595879102591425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387112501310185</v>
+        <v>0.02414775005308911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03107166598783806</v>
+        <v>0.03019675001269206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02505975001258776</v>
+        <v>0.02470429200911894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02606470801401883</v>
+        <v>0.02611933299340308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02353412500815466</v>
+        <v>0.0231068329885602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03312974999425933</v>
+        <v>0.03276858304161578</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01934195897774771</v>
+        <v>0.01929050002945587</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02833237504819408</v>
+        <v>0.02888020902173594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02395299996715039</v>
+        <v>0.02426670800196007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02701554098166525</v>
+        <v>0.02655033301562071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02936887502437457</v>
+        <v>0.02879095799289644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02571095799794421</v>
+        <v>0.02729175001149997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02297791698947549</v>
+        <v>0.0243383749620989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320739169837907</v>
+        <v>0.03112449997570366</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0220959999714978</v>
+        <v>0.02230504195904359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0230242499965243</v>
+        <v>0.02254854200873524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02499249996617436</v>
+        <v>0.02527749998262152</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02555074996780604</v>
+        <v>0.02461516601033509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0248879169812426</v>
+        <v>0.0245061669847928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02508354099700227</v>
+        <v>0.02458812500117347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02876783401006833</v>
+        <v>0.03081479197135195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01819329202407971</v>
+        <v>0.01895016699563712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02755216602236032</v>
+        <v>0.02893329202197492</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02206187497358769</v>
+        <v>0.02291904098819941</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0261424999916926</v>
+        <v>0.03522983397124335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs7_GRID13/tour/UAVs7_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs7_GRID13/tour/UAVs7_GRID13_1920_16_Greedy_sequences.xlsx
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02852812496712431</v>
+        <v>0.027011499973014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01897354196989909</v>
+        <v>0.0187269999878481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911925001535565</v>
+        <v>0.02870233298745006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330266596982256</v>
+        <v>0.02318462496623397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02339345903601497</v>
+        <v>0.02348470798460767</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02857024996774271</v>
+        <v>0.0283505410188809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02555333299096674</v>
+        <v>0.02539079205598682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03203679202124476</v>
+        <v>0.03190091700525954</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0302285419893451</v>
+        <v>0.03020624996861443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03372145799221471</v>
+        <v>0.03336612501880154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02658058301312849</v>
+        <v>0.02625904098385945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01939066703198478</v>
+        <v>0.01926337496843189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02140924998093396</v>
+        <v>0.02097524999408051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252443749923259</v>
+        <v>0.02322608401300386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02933533402392641</v>
+        <v>0.0281994590186514</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02849187498213723</v>
+        <v>0.02820004202658311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02431420801440254</v>
+        <v>0.02305316698038951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02578016702318564</v>
+        <v>0.02458658302202821</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02154920803150162</v>
+        <v>0.0203745830222033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02216866600792855</v>
+        <v>0.02223600004799664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02485666604479775</v>
+        <v>0.02464183297706768</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02986958401743323</v>
+        <v>0.02908104099333286</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02219666697783396</v>
+        <v>0.02175033400999382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02972183300880715</v>
+        <v>0.02887949999421835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02358320803614333</v>
+        <v>0.0227119589690119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04944491700734943</v>
+        <v>0.02735804195981473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598287496948615</v>
+        <v>0.02389595902059227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03095074999146163</v>
+        <v>0.02957250003237277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02550279203569517</v>
+        <v>0.02362050005467609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03195412497734651</v>
+        <v>0.03176804096437991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02267245895927772</v>
+        <v>0.02264725003624335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0279294170322828</v>
+        <v>0.02690545795485377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02425133297219872</v>
+        <v>0.0242494170088321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02588825003476813</v>
+        <v>0.02556366595672444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03018983302172273</v>
+        <v>0.02918645902536809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0237080420483835</v>
+        <v>0.02359083399642259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02656441699946299</v>
+        <v>0.02692758303601295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02877283398993313</v>
+        <v>0.02646725001977757</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02457995899021626</v>
+        <v>0.02270058303838596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401875000214204</v>
+        <v>0.02370545803569257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02454429201316088</v>
+        <v>0.02249812497757375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02123129100073129</v>
+        <v>0.02070466597797349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0211400410044007</v>
+        <v>0.01997545798076317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02739004197064787</v>
+        <v>0.02621583302970976</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03163108398439363</v>
+        <v>0.03093204199103639</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03179404098773375</v>
+        <v>0.02896041702479124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02764237497467548</v>
+        <v>0.02616095804842189</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0251111249672249</v>
+        <v>0.0237890409771353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02512137498706579</v>
+        <v>0.02529433299787343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03190458397148177</v>
+        <v>0.02982549997977912</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02628262504003942</v>
+        <v>0.02555995795410126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02713574998779222</v>
+        <v>0.02674866700544953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01829141698544845</v>
+        <v>0.01816070801578462</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02545687498059124</v>
+        <v>0.02554941701237112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02600558404810727</v>
+        <v>0.0251069160294719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02497183397645131</v>
+        <v>0.02445533301215619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0239355830126442</v>
+        <v>0.0224763749865815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02783191698836163</v>
+        <v>0.02785675000632182</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03186837502289563</v>
+        <v>0.03127704100916162</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02364387502893806</v>
+        <v>0.02319916698615998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02974949998315424</v>
+        <v>0.03004000004148111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02305916702607647</v>
+        <v>0.02292212500469759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02459537499817088</v>
+        <v>0.02404470799956471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02201074996264651</v>
+        <v>0.02029579202644527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03043645800789818</v>
+        <v>0.02868066600058228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02690733299823478</v>
+        <v>0.02862108300905675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02887920796638355</v>
+        <v>0.02707299997564405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02733545901719481</v>
+        <v>0.02532354200957343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03215612500207499</v>
+        <v>0.03166479204082862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387554198503494</v>
+        <v>0.02238087501609698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03116479102754965</v>
+        <v>0.03050620801514015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02964449999853969</v>
+        <v>0.02792862500064075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03816629201173782</v>
+        <v>0.03474933397956192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02985245804302394</v>
+        <v>0.03064112504944205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02595879102591425</v>
+        <v>0.02579166705254465</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02414775005308911</v>
+        <v>0.02349933300865814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03019675001269206</v>
+        <v>0.03039499995065853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02470429200911894</v>
+        <v>0.0243552919710055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02611933299340308</v>
+        <v>0.02511716703884304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0231068329885602</v>
+        <v>0.02325825003208593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03276858304161578</v>
+        <v>0.03261758299777284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01929050002945587</v>
+        <v>0.0190122919739224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02888020902173594</v>
+        <v>0.0281964170280844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02426670800196007</v>
+        <v>0.02381708304164931</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02655033301562071</v>
+        <v>0.02657704200828448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02879095799289644</v>
+        <v>0.02833087497856468</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02729175001149997</v>
+        <v>0.02513595798518509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0243383749620989</v>
+        <v>0.02341516601154581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03112449997570366</v>
+        <v>0.03115016600349918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02230504195904359</v>
+        <v>0.02127912500873208</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254854200873524</v>
+        <v>0.02245404198765755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02527749998262152</v>
+        <v>0.02812166599323973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02461516601033509</v>
+        <v>0.0244292090064846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0245061669847928</v>
+        <v>0.02484041597926989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02458812500117347</v>
+        <v>0.02485054201679304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03081479197135195</v>
+        <v>0.02829370799008757</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01895016699563712</v>
+        <v>0.01769037498161197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02893329202197492</v>
+        <v>0.02731295896228403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02291904098819941</v>
+        <v>0.02201154100475833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03522983397124335</v>
+        <v>0.0253694590064697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
